--- a/template/horaire.xlsx
+++ b/template/horaire.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/etiennerivard/notes_de_cours/piratage/template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5676A42-7F30-2846-B7F0-16CCA150B23D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CD83411-2E8F-DB45-8A87-A94E96AA1306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="340" yWindow="760" windowWidth="16360" windowHeight="17600" xr2:uid="{4696F4E7-E751-AB46-8D30-A385E7EE1466}"/>
   </bookViews>
@@ -632,7 +632,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="3">
-        <v>45891.635416666664</v>
+        <v>46255.510416666664</v>
       </c>
       <c r="D2" t="s">
         <v>48</v>
@@ -649,7 +649,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="4">
-        <v>45895.59375</v>
+        <v>46260.635416666664</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>13</v>
@@ -666,7 +666,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="3">
-        <v>45898.635416666664</v>
+        <v>46262.510416666664</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>14</v>
@@ -683,7 +683,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="4">
-        <v>45902.59375</v>
+        <v>46267.635416666664</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>16</v>
@@ -700,7 +700,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="3">
-        <v>45905.635416666664</v>
+        <v>46269.510416666664</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>18</v>
@@ -717,7 +717,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="4">
-        <v>45912.59375</v>
+        <v>46274.635416666664</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>5</v>
@@ -731,7 +731,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="3">
-        <v>45916.59375</v>
+        <v>46281.635416666664</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>20</v>
@@ -748,7 +748,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="4">
-        <v>45919.635416666664</v>
+        <v>46283.510416666664</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>22</v>
@@ -765,7 +765,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="3">
-        <v>45923.59375</v>
+        <v>46288.635416666664</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>24</v>
@@ -782,7 +782,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="4">
-        <v>45926.635416666664</v>
+        <v>46290.510416666664</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>31</v>
@@ -799,7 +799,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="3">
-        <v>45930.59375</v>
+        <v>46295.635416666664</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>42</v>
@@ -816,7 +816,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="4">
-        <v>45933.635416666664</v>
+        <v>46297.510416666664</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>44</v>
@@ -833,7 +833,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="3">
-        <v>45937.59375</v>
+        <v>46302.635416666664</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>28</v>
@@ -850,7 +850,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="4">
-        <v>45940.635416666664</v>
+        <v>46304.510416666664</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>36</v>
@@ -867,7 +867,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="3">
-        <v>45951.59375</v>
+        <v>46316.635416666664</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>6</v>
@@ -884,7 +884,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="4">
-        <v>45954.635416666664</v>
+        <v>46318.510416666664</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>6</v>
@@ -901,7 +901,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="3">
-        <v>45958.59375</v>
+        <v>46323.635416666664</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>6</v>
@@ -918,7 +918,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="4">
-        <v>45961.635416666664</v>
+        <v>46325.510416666664</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>33</v>
@@ -935,7 +935,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="3">
-        <v>45965.59375</v>
+        <v>46332.510416666664</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>34</v>
@@ -952,7 +952,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="4">
-        <v>45968.635416666664</v>
+        <v>46336.635416666664</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>40</v>
@@ -969,7 +969,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="3">
-        <v>45972.59375</v>
+        <v>46337.635416666664</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>26</v>
@@ -986,7 +986,7 @@
         <v>22</v>
       </c>
       <c r="C23" s="4">
-        <v>45975.635416666664</v>
+        <v>46339.510416666664</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>38</v>
@@ -1003,7 +1003,7 @@
         <v>23</v>
       </c>
       <c r="C24" s="3">
-        <v>45979.59375</v>
+        <v>46344.635416666664</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>46</v>
@@ -1020,7 +1020,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="4">
-        <v>45982.635416666664</v>
+        <v>46346.510416666664</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>8</v>
@@ -1034,7 +1034,7 @@
         <v>25</v>
       </c>
       <c r="C26" s="3">
-        <v>45986.59375</v>
+        <v>46351.635416666664</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>50</v>
@@ -1051,7 +1051,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="4">
-        <v>45989.635416666664</v>
+        <v>46353.510416666664</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>9</v>
@@ -1068,7 +1068,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="3">
-        <v>45993.59375</v>
+        <v>46358.635416666664</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>9</v>
@@ -1085,7 +1085,7 @@
         <v>28</v>
       </c>
       <c r="C29" s="4">
-        <v>45996.635416666664</v>
+        <v>46360.510416666664</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>9</v>
@@ -1102,7 +1102,7 @@
         <v>29</v>
       </c>
       <c r="C30" s="3">
-        <v>46000.59375</v>
+        <v>46365.635416666664</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>10</v>
@@ -1119,7 +1119,7 @@
         <v>30</v>
       </c>
       <c r="C31" s="5">
-        <v>46003.635416666664</v>
+        <v>46367.510416666664</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>11</v>
